--- a/DataVaryingTemperature/LBracketMaterialsThermal.xlsx
+++ b/DataVaryingTemperature/LBracketMaterialsThermal.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\MaterialTemperature\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\DataVaryingTemperature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D820E17-432B-4577-823A-1EB1B073D8FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C86B02-92C8-4158-8F02-73FDD0CA7C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1776" windowWidth="20604" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,10 +22,21 @@
     <definedName name="Yield_Strength">Reference!$B$5:$D$5</definedName>
     <definedName name="Youngs_Modulus">Reference!$B$3:$D$3</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -526,8 +537,8 @@
     <col min="1" max="1" width="20.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="11.6640625" style="1" customWidth="1"/>
@@ -698,7 +709,7 @@
         <v>73000000000</v>
       </c>
       <c r="E5" s="6">
-        <v>3000000</v>
+        <v>-40000000000</v>
       </c>
       <c r="F5" s="8">
         <v>-6</v>
